--- a/spreadsheets/raw_data/raw_data.xlsx
+++ b/spreadsheets/raw_data/raw_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mauricio.pontes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\scripts_python\estruturacaoBoletim\generic-data-transformer\spreadsheets\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36866FAE-3DAB-4668-B207-6FA211FC4AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B07EB27-62E1-4A9E-B3BD-E7EB1E5A9DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{4AD1315D-1C8E-4FC3-890A-4AFE789B4C7A}"/>
+    <workbookView xWindow="3225" yWindow="-13935" windowWidth="21600" windowHeight="11835" xr2:uid="{4AD1315D-1C8E-4FC3-890A-4AFE789B4C7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Estrutura Atual " sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="64">
   <si>
     <t>Investidor Geral</t>
   </si>
@@ -214,6 +214,21 @@
   </si>
   <si>
     <t>Segmento</t>
+  </si>
+  <si>
+    <t>102% CDI</t>
+  </si>
+  <si>
+    <t>103% CDI</t>
+  </si>
+  <si>
+    <t>104% CDI</t>
+  </si>
+  <si>
+    <t>105% CDI</t>
+  </si>
+  <si>
+    <t>106% CDI</t>
   </si>
 </sst>
 </file>
@@ -790,6 +805,21 @@
       <c r="V3" t="s">
         <v>3</v>
       </c>
+      <c r="W3" t="s">
+        <v>59</v>
+      </c>
+      <c r="X3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>63</v>
+      </c>
       <c r="AB3" t="s">
         <v>2</v>
       </c>
